--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/PRODUCTION SCHEDULE/Lâm Sup/PROJECT LÂM/REPORT DAILY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv_ortholite_vn/Documents/PROJECT LÂM/REPORT DAILY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F7D20E-8C98-4304-B83A-B144562E067D}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55CD8D96-3083-4301-B311-1250507EA079}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Số sheet/bun</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Tổng độ dày bun sau tách (mm)</t>
+  </si>
+  <si>
+    <t>Dung sai (mm)</t>
   </si>
 </sst>
 </file>
@@ -113,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -121,6 +124,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -402,16 +408,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -419,13 +426,17 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -433,15 +444,18 @@
         <v>144</v>
       </c>
       <c r="C2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="2">
         <f>+B2/A2</f>
         <v>72</v>
       </c>
-      <c r="D2" s="2">
-        <f>ROUNDDOWN((B2/(A2-0.2)),0)</f>
+      <c r="E2" s="2">
+        <f>ROUNDUP((B2/(A2-C2)),0)</f>
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2.5</v>
       </c>
@@ -449,15 +463,18 @@
         <v>140</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3:C21" si="0">+B3/A3</f>
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D21" si="0">+B3/A3</f>
         <v>56</v>
       </c>
-      <c r="D3" s="2">
-        <f t="shared" ref="D3:D21" si="1">ROUNDDOWN((B3/(A3-0.2)),0)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E21" si="1">ROUNDUP((B3/(A3-C3)),0)</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -465,15 +482,18 @@
         <v>144</v>
       </c>
       <c r="C4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="D4" s="2">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E4" s="2">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>3.5</v>
       </c>
@@ -481,15 +501,18 @@
         <v>140</v>
       </c>
       <c r="C5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="D5" s="2">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E5" s="2">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -497,15 +520,18 @@
         <v>140</v>
       </c>
       <c r="C6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="D6" s="2">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E6" s="2">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>4.2</v>
       </c>
@@ -513,15 +539,18 @@
         <v>142.80000000000001</v>
       </c>
       <c r="C7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="D7" s="2">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E7" s="2">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>4.5</v>
       </c>
@@ -529,15 +558,18 @@
         <v>139.5</v>
       </c>
       <c r="C8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="D8" s="2">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E8" s="2">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -545,15 +577,18 @@
         <v>140</v>
       </c>
       <c r="C9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="D9" s="2">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E9" s="2">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>5.2</v>
       </c>
@@ -561,15 +596,18 @@
         <v>140.4</v>
       </c>
       <c r="C10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="D10" s="2">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E10" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>5.5</v>
       </c>
@@ -577,15 +615,18 @@
         <v>138.5</v>
       </c>
       <c r="C11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="2">
         <f t="shared" si="0"/>
         <v>25.181818181818183</v>
       </c>
-      <c r="D11" s="2">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E11" s="2">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>6</v>
       </c>
@@ -593,15 +634,18 @@
         <v>138</v>
       </c>
       <c r="C12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="D12" s="2">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E12" s="2">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>7</v>
       </c>
@@ -609,15 +653,18 @@
         <v>140</v>
       </c>
       <c r="C13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D13" s="2">
-        <f>ROUNDDOWN((B13/(A13-0.2)),0)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E13" s="2">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>8</v>
       </c>
@@ -625,15 +672,18 @@
         <v>136</v>
       </c>
       <c r="C14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="D14" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>8.1999999999999993</v>
       </c>
@@ -641,15 +691,18 @@
         <v>139.4</v>
       </c>
       <c r="C15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="2">
         <f t="shared" si="0"/>
         <v>17.000000000000004</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -657,15 +710,18 @@
         <v>140</v>
       </c>
       <c r="C16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="D16" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -673,15 +729,18 @@
         <v>140</v>
       </c>
       <c r="C17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="2">
         <f t="shared" si="0"/>
         <v>12.727272727272727</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E17" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -689,15 +748,18 @@
         <v>144</v>
       </c>
       <c r="C18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="D18" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E18" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -705,15 +767,18 @@
         <v>143</v>
       </c>
       <c r="C19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D19" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E19" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>13.5</v>
       </c>
@@ -721,15 +786,18 @@
         <v>135</v>
       </c>
       <c r="C20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D20" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E20" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -737,19 +805,23 @@
         <v>140</v>
       </c>
       <c r="C21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D21" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D21" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E21" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -770,6 +842,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca0a34949405af18a2a1038fedd5973f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56f3efbd08470b89beac8b88620aafc3" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1036,15 +1117,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
   <ds:schemaRefs>
@@ -1057,6 +1129,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F799538-D688-4B64-8214-56F45057B7B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1073,12 +1153,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -125,7 +125,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,15 +842,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca0a34949405af18a2a1038fedd5973f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56f3efbd08470b89beac8b88620aafc3" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1117,6 +1108,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
   <ds:schemaRefs>
@@ -1129,14 +1129,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F799538-D688-4B64-8214-56F45057B7B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1153,4 +1145,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv_ortholite_vn/Documents/PROJECT LÂM/REPORT DAILY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55CD8D96-3083-4301-B311-1250507EA079}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54D6EA22-4355-4780-881A-662BE078902E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,17 +47,20 @@
     <t>Số sheet/bun tối ưu</t>
   </si>
   <si>
-    <t>Tổng độ dày bun sau tách (mm)</t>
+    <t>Dung sai (mm)</t>
   </si>
   <si>
-    <t>Dung sai (mm)</t>
+    <t>Độ dày bun sau tách da tham chiếu (mm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +78,13 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,10 +123,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -128,8 +139,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -408,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.77734375" style="1" customWidth="1"/>
@@ -418,15 +433,15 @@
     <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -434,9 +449,9 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -444,37 +459,35 @@
         <v>144</v>
       </c>
       <c r="C2" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
         <f>+B2/A2</f>
         <v>72</v>
       </c>
-      <c r="E2" s="2">
-        <f>ROUNDUP((B2/(A2-C2)),0)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E2" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2.5</v>
       </c>
       <c r="B3" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C3" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D21" si="0">+B3/A3</f>
-        <v>56</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" ref="E3:E21" si="1">ROUNDUP((B3/(A3-C3)),0)</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="E3" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -482,227 +495,215 @@
         <v>144</v>
       </c>
       <c r="C4" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E4" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>3.5</v>
       </c>
       <c r="B5" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>41.142857142857146</v>
+      </c>
+      <c r="E5" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C6" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="E6" s="2">
-        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="E6" s="5">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>4.2</v>
       </c>
       <c r="B7" s="2">
-        <v>142.80000000000001</v>
+        <v>144</v>
       </c>
       <c r="C7" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>34.285714285714285</v>
+      </c>
+      <c r="E7" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>4.5</v>
       </c>
       <c r="B8" s="2">
-        <v>139.5</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>5.2</v>
       </c>
       <c r="B10" s="2">
-        <v>140.4</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="E10" s="2">
-        <f t="shared" si="1"/>
+        <v>27.884615384615383</v>
+      </c>
+      <c r="E10" s="5">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>5.5</v>
       </c>
       <c r="B11" s="2">
-        <v>138.5</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>25.181818181818183</v>
-      </c>
-      <c r="E11" s="2">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>26.363636363636363</v>
+      </c>
+      <c r="E11" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>6</v>
       </c>
       <c r="B12" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="E12" s="2">
-        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E12" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>7</v>
       </c>
       <c r="B13" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C13" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E13" s="2">
-        <f t="shared" si="1"/>
+        <v>20.857142857142858</v>
+      </c>
+      <c r="E13" s="5">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>8</v>
       </c>
       <c r="B14" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2">
         <v>0.2</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E14" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>8.1999999999999993</v>
       </c>
       <c r="B15" s="2">
-        <v>139.4</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2">
         <v>0.2</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="0"/>
-        <v>17.000000000000004</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="1"/>
+        <v>17.560975609756099</v>
+      </c>
+      <c r="E15" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -716,9 +717,8 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E16" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
+      <c r="E16" s="5">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
@@ -726,17 +726,16 @@
         <v>11</v>
       </c>
       <c r="B17" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2">
         <v>0.2</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="0"/>
-        <v>12.727272727272727</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E17" s="5">
         <v>13</v>
       </c>
     </row>
@@ -754,9 +753,8 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E18" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
+      <c r="E18" s="5">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
@@ -773,9 +771,8 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E19" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
+      <c r="E19" s="5">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
@@ -792,9 +789,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E20" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
+      <c r="E20" s="5">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
@@ -811,9 +807,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E21" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
+      <c r="E21" s="5">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -830,15 +825,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1109,21 +1101,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1148,9 +1140,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv_ortholite_vn/Documents/PROJECT LÂM/REPORT DAILY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54D6EA22-4355-4780-881A-662BE078902E}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5973359-1DEE-4957-90F3-D8F82A29C1B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Số sheet/bun</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Độ dày bun sau tách da tham chiếu (mm)</t>
+  </si>
+  <si>
+    <t>Bán Thành Phẩm</t>
   </si>
 </sst>
 </file>
@@ -91,12 +94,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -136,10 +145,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -431,6 +440,7 @@
     <col min="3" max="3" width="21.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -449,7 +459,9 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
@@ -465,8 +477,12 @@
         <f>+B2/A2</f>
         <v>72</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>72</v>
+      </c>
+      <c r="F2" s="4">
+        <f>E2/2</f>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -483,8 +499,12 @@
         <f t="shared" ref="D3:D21" si="0">+B3/A3</f>
         <v>58</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>58</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" ref="F3:F21" si="1">E3/2</f>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -501,8 +521,12 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>48</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -519,8 +543,12 @@
         <f t="shared" si="0"/>
         <v>41.142857142857146</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>41</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
@@ -537,8 +565,12 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>37</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -555,8 +587,12 @@
         <f t="shared" si="0"/>
         <v>34.285714285714285</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>35</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -567,14 +603,18 @@
         <v>144</v>
       </c>
       <c r="C8" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>32</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -585,14 +625,18 @@
         <v>145</v>
       </c>
       <c r="C9" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>29</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
@@ -612,6 +656,10 @@
       <c r="E10" s="5">
         <v>29</v>
       </c>
+      <c r="F10" s="4">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
@@ -621,14 +669,18 @@
         <v>145</v>
       </c>
       <c r="C11" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="0"/>
         <v>26.363636363636363</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>26</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
@@ -639,14 +691,18 @@
         <v>144</v>
       </c>
       <c r="C12" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>24</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
@@ -663,8 +719,12 @@
         <f t="shared" si="0"/>
         <v>20.857142857142858</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>21</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
@@ -675,14 +735,18 @@
         <v>144</v>
       </c>
       <c r="C14" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>18</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
@@ -699,8 +763,12 @@
         <f t="shared" si="0"/>
         <v>17.560975609756099</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>18</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
@@ -711,17 +779,21 @@
         <v>140</v>
       </c>
       <c r="C16" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F16" s="4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -729,17 +801,21 @@
         <v>143</v>
       </c>
       <c r="C17" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17" s="4">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -747,17 +823,21 @@
         <v>144</v>
       </c>
       <c r="C18" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -765,17 +845,21 @@
         <v>143</v>
       </c>
       <c r="C19" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F19" s="4">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>13.5</v>
       </c>
@@ -783,17 +867,21 @@
         <v>135</v>
       </c>
       <c r="C20" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F20" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -801,17 +889,21 @@
         <v>140</v>
       </c>
       <c r="C21" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F21" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -825,15 +917,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca0a34949405af18a2a1038fedd5973f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56f3efbd08470b89beac8b88620aafc3" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1100,7 +1183,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
@@ -1112,15 +1195,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F799538-D688-4B64-8214-56F45057B7B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1139,7 +1223,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1148,4 +1232,12 @@
     <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -1184,6 +1184,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
@@ -1193,15 +1202,6 @@
     <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1224,6 +1224,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1232,12 +1240,4 @@
     <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv_ortholite_vn/Documents/PROJECT LÂM/REPORT DAILY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5973359-1DEE-4957-90F3-D8F82A29C1B4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,17 +433,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.36328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="42.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -463,7 +463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -485,7 +485,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A3" s="2">
         <v>2.5</v>
       </c>
@@ -507,7 +507,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -529,7 +529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A5" s="2">
         <v>3.5</v>
       </c>
@@ -551,7 +551,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A7" s="2">
         <v>4.2</v>
       </c>
@@ -595,7 +595,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A8" s="2">
         <v>4.5</v>
       </c>
@@ -617,7 +617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -639,7 +639,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A10" s="2">
         <v>5.2</v>
       </c>
@@ -661,7 +661,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A11" s="2">
         <v>5.5</v>
       </c>
@@ -683,7 +683,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A12" s="2">
         <v>6</v>
       </c>
@@ -705,7 +705,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A13" s="2">
         <v>7</v>
       </c>
@@ -727,7 +727,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A14" s="2">
         <v>8</v>
       </c>
@@ -749,7 +749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A15" s="2">
         <v>8.1999999999999993</v>
       </c>
@@ -771,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -793,7 +793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -815,7 +815,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -837,7 +837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A19" s="2">
         <v>13</v>
       </c>
@@ -859,7 +859,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A20" s="2">
         <v>13.5</v>
       </c>
@@ -881,7 +881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -903,7 +903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -917,6 +917,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca0a34949405af18a2a1038fedd5973f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56f3efbd08470b89beac8b88620aafc3" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1183,28 +1204,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F799538-D688-4B64-8214-56F45057B7B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1221,23 +1240,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/độ dày - số tấm.xlsx
+++ b/độ dày - số tấm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam-my.sharepoint.com/personal/lam_dv2_ortholite_vn/Documents/PROJECT LÂM/DailyFoamingReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5973359-1DEE-4957-90F3-D8F82A29C1B4}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{B48CC9E5-40C6-4D72-B307-B41CD2202D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E74E6C-B9E4-49BD-AD06-B78B997FA7C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -917,27 +917,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca0a34949405af18a2a1038fedd5973f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56f3efbd08470b89beac8b88620aafc3" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1204,26 +1183,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F799538-D688-4B64-8214-56F45057B7B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1240,4 +1221,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB70DDE8-E8D5-47B5-B409-23108DE390AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90D36F7-D59D-4591-B3D9-58D7303A6F3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>